--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486472_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486472_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6064</v>
+        <v>2.0371</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1905</v>
+        <v>1.8061</v>
       </c>
       <c r="F2" t="n">
-        <v>0.416</v>
+        <v>0.231</v>
       </c>
       <c r="G2" t="n">
         <v>0.0008</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1924</v>
+        <v>0.6231</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1138</v>
+        <v>0.7294</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0786</v>
+        <v>-0.1064</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5443</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.9157</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.4642</v>
+        <v>2.0909</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0141</v>
+        <v>-1.1752</v>
       </c>
       <c r="G3" t="n">
-        <v>1.108</v>
+        <v>3.3035</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.873</v>
+        <v>1.5177</v>
       </c>
       <c r="I3" t="n">
-        <v>1.981</v>
+        <v>1.7858</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0308</v>
+        <v>4.2272</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6721</v>
+        <v>2.0836</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7029</v>
+        <v>2.1436</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0772</v>
+        <v>-0.9237</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2009</v>
+        <v>-0.5659</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2781</v>
+        <v>-0.3578</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.435</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R3" t="n">
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0514</v>
+        <v>-0.8652</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1454</v>
+        <v>-0.0036</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1968</v>
+        <v>-0.8616</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1745</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4855</v>
+        <v>0.5568</v>
       </c>
       <c r="E4" t="n">
-        <v>0.534</v>
+        <v>-1.3957</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0486</v>
+        <v>1.9524</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9286</v>
+        <v>1.108</v>
       </c>
       <c r="H4" t="n">
-        <v>0.736</v>
+        <v>-0.873</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6647</v>
+        <v>1.981</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2605</v>
+        <v>1.0308</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3354</v>
+        <v>-0.6721</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.07489999999999999</v>
+        <v>1.7029</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1891</v>
+        <v>0.0772</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5994</v>
+        <v>-0.2009</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5898</v>
+        <v>0.2781</v>
       </c>
       <c r="P4" t="n">
         <v>-0.435</v>
@@ -766,19 +766,19 @@
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1542</v>
+        <v>0.0583</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2463</v>
+        <v>-0.0769</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4005</v>
+        <v>0.1352</v>
       </c>
       <c r="V4" t="n">
-        <v>1.695</v>
+        <v>-0.1745</v>
       </c>
       <c r="W4" t="n">
-        <v>1.695</v>
+        <v>-0.1745</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3338</v>
+        <v>0.4067</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7557</v>
+        <v>0.671</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4218</v>
+        <v>-0.2643</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3035</v>
+        <v>-0.9286</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5177</v>
+        <v>0.736</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7858</v>
+        <v>-1.6647</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2272</v>
+        <v>1.2605</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0836</v>
+        <v>1.3354</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1436</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9237</v>
+        <v>-2.1891</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5659</v>
+        <v>-0.5994</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3578</v>
+        <v>-1.5898</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5225</v>
+        <v>-0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
         <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4471</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3389</v>
+        <v>-0.1093</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1082</v>
+        <v>0.1847</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0197</v>
+        <v>-0.1324</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01</v>
+        <v>-0.2568</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0297</v>
+        <v>0.1245</v>
       </c>
       <c r="G6" t="n">
         <v>-1.109</v>
@@ -922,13 +922,13 @@
         <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4368</v>
+        <v>0.3242</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4831</v>
+        <v>0.2163</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0463</v>
+        <v>0.1078</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5808</v>
+        <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9328</v>
+        <v>0.0197</v>
       </c>
       <c r="F7" t="n">
-        <v>0.352</v>
+        <v>-0.1697</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.662</v>
+        <v>-1.1146</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2109</v>
+        <v>0.0608</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4511</v>
+        <v>-1.1754</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.0737</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.3415</v>
+        <v>-0.6173</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2677</v>
+        <v>0.0765</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5882</v>
+        <v>-0.5738</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1306</v>
+        <v>0.6781</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7188</v>
+        <v>-1.2519</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3635</v>
+        <v>-0.3182</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9458</v>
+        <v>0.3653</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4177</v>
+        <v>-0.6835</v>
       </c>
       <c r="V7" t="n">
         <v>0.1952</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>J. PERIS CRESPO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9245</v>
+        <v>-1.4934</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5391</v>
+        <v>-2.6143</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3855</v>
+        <v>1.1209</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1146</v>
+        <v>-3.2425</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0608</v>
+        <v>-2.1166</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1754</v>
+        <v>-1.1259</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-2.7348</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6173</v>
+        <v>-2.0313</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0765</v>
+        <v>-0.7036</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5738</v>
+        <v>-0.5077</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6781</v>
+        <v>-0.0854</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2519</v>
+        <v>-0.4224</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0927</v>
+        <v>-0.2509</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1935</v>
+        <v>0.0781</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8992</v>
+        <v>-0.329</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PERIS CRESPO</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.503</v>
+        <v>-1.5729</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2848</v>
+        <v>-1.8016</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.2287</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2425</v>
+        <v>-3.662</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1166</v>
+        <v>-2.2109</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1259</v>
+        <v>-1.4511</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7348</v>
+        <v>-2.0737</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0313</v>
+        <v>-2.3415</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7036</v>
+        <v>0.2677</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5077</v>
+        <v>-1.5882</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0854</v>
+        <v>0.1306</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4224</v>
+        <v>-1.7188</v>
       </c>
       <c r="P9" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2605</v>
+        <v>0.3713</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5924</v>
+        <v>0.0769</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.668</v>
+        <v>0.2944</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7667</v>
+        <v>-2.4476</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0429</v>
+        <v>0.5844</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7238</v>
+        <v>-3.032</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7002</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6766</v>
+        <v>-0.3575</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0154</v>
+        <v>-0.3881</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3389</v>
+        <v>0.0306</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2599</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1818</v>
+        <v>-2.5284</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3132</v>
+        <v>1.1207</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.495</v>
+        <v>-3.6491</v>
       </c>
       <c r="G11" t="n">
         <v>0.3913</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1833</v>
+        <v>0.4702</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6609</v>
+        <v>0.1466</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4777</v>
+        <v>0.3235</v>
       </c>
       <c r="V11" t="n">
         <v>-3.3899</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.7294</v>
+        <v>-10.6369</v>
       </c>
       <c r="E12" t="n">
         <v>-5.7998</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.9296</v>
+        <v>-4.8371</v>
       </c>
       <c r="G12" t="n">
         <v>-4.832</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0703</v>
+        <v>-0.9779</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1334</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.8445</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4345</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.7303</v>
+        <v>-15.0453</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.2602</v>
+        <v>-5.5754</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.470099999999999</v>
+        <v>-9.469899999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-10.7853</v>
@@ -1441,7 +1441,7 @@
         <v>-2.7572</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8619000000000003</v>
+        <v>0.8618999999999994</v>
       </c>
       <c r="K13" t="n">
         <v>-8.2544</v>
@@ -1453,7 +1453,7 @@
         <v>-11.6471</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2260000000000002</v>
+        <v>0.226</v>
       </c>
       <c r="O13" t="n">
         <v>-11.8734</v>
@@ -1468,13 +1468,13 @@
         <v>15.2255</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5322</v>
+        <v>-0.8472</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2165000000000001</v>
+        <v>0.9013000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.7485</v>
+        <v>-1.7488</v>
       </c>
       <c r="V13" t="n">
         <v>-5.5877</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9911</v>
+        <v>5.3366</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7265</v>
+        <v>3.6148</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2645</v>
+        <v>1.7218</v>
       </c>
       <c r="G14" t="n">
         <v>5.1439</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6525</v>
+        <v>0.998</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8857</v>
+        <v>0.7739</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2331</v>
+        <v>0.2241</v>
       </c>
       <c r="V14" t="n">
         <v>0.9347</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0351</v>
+        <v>4.2701</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5426</v>
+        <v>2.3148</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5075</v>
+        <v>1.9553</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1344</v>
+        <v>-1.2589</v>
       </c>
       <c r="H15" t="n">
-        <v>1.195</v>
+        <v>0.9396</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0606</v>
+        <v>-2.1985</v>
       </c>
       <c r="J15" t="n">
-        <v>1.945</v>
+        <v>-1.4453</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9671999999999999</v>
+        <v>-0.0516</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9778</v>
+        <v>-1.3937</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8106</v>
+        <v>0.1863</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2277</v>
+        <v>0.9912</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0383</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9437</v>
+        <v>0.8117</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4252</v>
+        <v>0.5876</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4815</v>
+        <v>0.2241</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3045</v>
+        <v>3.1947</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2599</v>
+        <v>3.3899</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.9554</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5867</v>
+        <v>3.6806</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8678</v>
+        <v>3.6486</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7189</v>
+        <v>0.032</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2589</v>
+        <v>1.1344</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9396</v>
+        <v>1.195</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.1985</v>
+        <v>-0.0606</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.4453</v>
+        <v>1.945</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0516</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3937</v>
+        <v>0.9778</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1863</v>
+        <v>-0.8106</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9912</v>
+        <v>0.2277</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-1.0383</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1283</v>
+        <v>0.5891</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1406</v>
+        <v>0.5312</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0123</v>
+        <v>0.058</v>
       </c>
       <c r="V16" t="n">
-        <v>3.1947</v>
+        <v>1.3045</v>
       </c>
       <c r="W16" t="n">
-        <v>3.3899</v>
+        <v>2.2599</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1952</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2976</v>
+        <v>2.712</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3535</v>
+        <v>0.9065</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9441</v>
+        <v>1.8055</v>
       </c>
       <c r="G17" t="n">
         <v>1.93</v>
@@ -1780,13 +1780,13 @@
         <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>1.173</v>
+        <v>0.5873</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5432</v>
+        <v>0.0961</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6298</v>
+        <v>0.4912</v>
       </c>
       <c r="V17" t="n">
         <v>1.4997</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. BARTON</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7804</v>
+        <v>1.457</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0063</v>
+        <v>-1.9432</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7741</v>
+        <v>3.4002</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5218</v>
+        <v>2.8777</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4835</v>
+        <v>3.1781</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0382</v>
+        <v>-0.3004</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0747</v>
+        <v>1.6643</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0365</v>
+        <v>1.3933</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0382</v>
+        <v>0.271</v>
       </c>
       <c r="M18" t="n">
-        <v>0.447</v>
+        <v>1.2134</v>
       </c>
       <c r="N18" t="n">
-        <v>0.447</v>
+        <v>1.7848</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.5714</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.4801</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0411</v>
+        <v>0.1018</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1274</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1096</v>
+        <v>0.2292</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>C. BARTON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6323</v>
+        <v>0.9538</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1667</v>
+        <v>0.118</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7991</v>
+        <v>0.8358</v>
       </c>
       <c r="G19" t="n">
-        <v>2.8777</v>
+        <v>0.5218</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1781</v>
+        <v>0.4835</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3004</v>
+        <v>0.0382</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6643</v>
+        <v>0.0747</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3933</v>
+        <v>0.0365</v>
       </c>
       <c r="L19" t="n">
-        <v>0.271</v>
+        <v>0.0382</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2134</v>
+        <v>0.447</v>
       </c>
       <c r="N19" t="n">
-        <v>1.7848</v>
+        <v>0.447</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5714</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4801</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9576</v>
+        <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7228</v>
+        <v>0.2145</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3509</v>
+        <v>0.0433</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3719</v>
+        <v>0.1712</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3915</v>
+        <v>0.4008</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1599</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5513</v>
+        <v>0.4008</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8121</v>
+        <v>0.298</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5627</v>
+        <v>0.298</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2494</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.0639</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.2169</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2518</v>
+        <v>0.298</v>
       </c>
       <c r="N20" t="n">
-        <v>1.6542</v>
+        <v>0.298</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4024</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4059</v>
+        <v>0.1027</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3975</v>
+        <v>0.1027</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3391</v>
+        <v>0.3786</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-1.3834</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3391</v>
+        <v>1.762</v>
       </c>
       <c r="G21" t="n">
-        <v>0.298</v>
+        <v>-0.8121</v>
       </c>
       <c r="H21" t="n">
-        <v>0.298</v>
+        <v>-0.5627</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.2494</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-2.0639</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-2.2169</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="M21" t="n">
-        <v>0.298</v>
+        <v>1.2518</v>
       </c>
       <c r="N21" t="n">
-        <v>0.298</v>
+        <v>1.6542</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.4024</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0411</v>
+        <v>-0.4188</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.2319</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0411</v>
+        <v>-0.1869</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.23</v>
+        <v>0.1883</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.8275</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.338</v>
+        <v>-0.6392</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6745</v>
+        <v>1.5395</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4045</v>
+        <v>0.1825</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.079</v>
+        <v>1.357</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0284</v>
+        <v>1.7492</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1246</v>
+        <v>-0.0302</v>
       </c>
       <c r="L22" t="n">
-        <v>0.153</v>
+        <v>1.7794</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7029</v>
+        <v>-0.2097</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5291</v>
+        <v>0.2127</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.232</v>
+        <v>-0.4224</v>
       </c>
       <c r="P22" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2519</v>
+        <v>0.3214</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5396</v>
+        <v>0.3833</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7124</v>
+        <v>-0.0619</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.8902</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4091</v>
+        <v>-0.1669</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0452</v>
+        <v>0.2327</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4543</v>
+        <v>-0.3996</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5395</v>
+        <v>-0.6745</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1825</v>
+        <v>0.4045</v>
       </c>
       <c r="I23" t="n">
-        <v>1.357</v>
+        <v>-1.079</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7492</v>
+        <v>0.0284</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0302</v>
+        <v>-0.1246</v>
       </c>
       <c r="L23" t="n">
-        <v>1.7794</v>
+        <v>0.153</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2097</v>
+        <v>-0.7029</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2127</v>
+        <v>0.5291</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4224</v>
+        <v>-1.232</v>
       </c>
       <c r="P23" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2759</v>
+        <v>0.855</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.399</v>
+        <v>0.2043</v>
       </c>
       <c r="U23" t="n">
-        <v>0.123</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8902</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.8902</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1445</v>
+        <v>-1.2453</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6867</v>
+        <v>1.1337</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8312</v>
+        <v>-2.379</v>
       </c>
       <c r="G24" t="n">
         <v>0.0856</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2948</v>
+        <v>-0.3957</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9589</v>
+        <v>-0.5119</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3359</v>
+        <v>0.1163</v>
       </c>
       <c r="V24" t="n">
         <v>0.3698</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>15.7302</v>
+        <v>17.9656</v>
       </c>
       <c r="E25" t="n">
         <v>9.469999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>6.2601</v>
+        <v>8.4956</v>
       </c>
       <c r="G25" t="n">
         <v>10.7854</v>
@@ -2380,19 +2380,19 @@
         <v>11.6471</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2262999999999998</v>
+        <v>-0.2263000000000001</v>
       </c>
       <c r="L25" t="n">
         <v>11.8734</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8618999999999997</v>
+        <v>-0.861899999999999</v>
       </c>
       <c r="N25" t="n">
         <v>8.254399999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.116299999999999</v>
+        <v>-9.116300000000001</v>
       </c>
       <c r="P25" t="n">
         <v>-2.1751</v>
@@ -2404,13 +2404,13 @@
         <v>13.0505</v>
       </c>
       <c r="S25" t="n">
-        <v>1.5322</v>
+        <v>3.767</v>
       </c>
       <c r="T25" t="n">
-        <v>1.7486</v>
+        <v>1.7485</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2162999999999999</v>
+        <v>2.0187</v>
       </c>
       <c r="V25" t="n">
         <v>5.5877</v>
@@ -2419,7 +2419,7 @@
         <v>11.2998</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.7118</v>
+        <v>-5.711799999999999</v>
       </c>
     </row>
   </sheetData>
